--- a/3er año/Noveno Semestre/horarios.xlsx
+++ b/3er año/Noveno Semestre/horarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\importante\Facultad\3er año\Noveno Semestre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A3865CF-DEDE-4D1B-BC03-964DBFB89C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535A8AA3-19E7-46B8-A12D-ACA35C2CF9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28200" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>Hora</t>
   </si>
@@ -107,6 +107,12 @@
     </r>
   </si>
   <si>
+    <t>AULA 5</t>
+  </si>
+  <si>
+    <t>AULA 1-1</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -126,11 +132,26 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> Lunes 16hs a 18hs - EXP Practica 18hs a 19hs</t>
     </r>
   </si>
   <si>
-    <t>Practica:</t>
+    <r>
+      <t xml:space="preserve">Practica: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Martes 17:30hs a 19hs</t>
+    </r>
+  </si>
+  <si>
+    <t>EXP PRACTICA</t>
   </si>
 </sst>
 </file>
@@ -209,7 +230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -337,11 +358,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -396,7 +448,23 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="15" customWidth="1"/>
@@ -737,11 +805,11 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="22"/>
-      <c r="J2" s="23"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -752,11 +820,13 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="H3" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="28"/>
-      <c r="J3" s="29"/>
+      <c r="H3" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="22"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="23"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -767,11 +837,11 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="H4" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="23"/>
+      <c r="H4" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="36"/>
+      <c r="J4" s="37"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -922,49 +992,55 @@
       <c r="A17" s="2">
         <v>0.64583333333333404</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="30">
         <v>0.66666666666666696</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="B18" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="6"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="M18" s="17"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="30">
         <v>0.6875</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="1"/>
       <c r="E19" s="7"/>
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="30">
         <v>0.70833333333333404</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="B20" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="9"/>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="30">
         <v>0.72916666666666696</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="31" t="s">
+        <v>10</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="10" t="s">
         <v>10</v>
@@ -976,8 +1052,10 @@
       <c r="A22" s="2">
         <v>0.75</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="B22" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="32"/>
       <c r="D22" s="5"/>
       <c r="E22" s="10"/>
       <c r="F22" s="6"/>
@@ -986,8 +1064,12 @@
       <c r="A23" s="2">
         <v>0.77083333333333404</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+      <c r="B23" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>16</v>
+      </c>
       <c r="D23" s="14"/>
       <c r="E23" s="10" t="s">
         <v>12</v>
@@ -998,9 +1080,9 @@
       <c r="A24" s="2">
         <v>0.79166666666666696</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="38"/>
       <c r="E24" s="10"/>
       <c r="F24" s="15"/>
     </row>
@@ -1009,7 +1091,7 @@
         <v>0.812500000000001</v>
       </c>
       <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="C25" s="16"/>
       <c r="D25" s="14"/>
       <c r="E25" s="11"/>
       <c r="F25" s="15"/>
@@ -1024,6 +1106,9 @@
       <c r="E26" s="16"/>
       <c r="F26" s="12"/>
     </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C32" s="34"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
